--- a/03_Outputs/all/01_TablasDescriptivas/idx15_vejez_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx15_vejez_vr.xlsx
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>8.397903188109593</v>
+        <v>8.397903188109588</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.707701851493494</v>
+        <v>1.707701851493491</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.5198032487372636</v>
+        <v>0.5198032487372641</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.2206080995670574</v>
+        <v>0.2206080995670575</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.06177935516730174</v>
+        <v>0.06177935516730183</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.05003215984055298</v>
+        <v>0.05003215984055306</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.03651336418512512</v>
+        <v>0.03651336418512506</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.005435436278774105</v>
+        <v>0.005435436278774112</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.0001074254275588517</v>
+        <v>0.0001074254275588514</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>8.82803057688097E-05</v>
+        <v>8.828030576880808E-05</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>2.759088751915867E-05</v>
+        <v>2.759088751915909E-05</v>
       </c>
       <c r="C12">
         <v>11</v>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>8.397903188109593</v>
+        <v>8.397903188109588</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>10.10560503960309</v>
+        <v>10.10560503960308</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>10.62540828834035</v>
+        <v>10.62540828834034</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>10.84601638790741</v>
+        <v>10.8460163879074</v>
       </c>
       <c r="C16">
         <v>4</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>10.90779574307471</v>
+        <v>10.9077957430747</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>10.99434126710039</v>
+        <v>10.99434126710038</v>
       </c>
       <c r="C19">
         <v>7</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>10.99977670337916</v>
+        <v>10.99977670337915</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>10.99988412880672</v>
+        <v>10.99988412880671</v>
       </c>
       <c r="C21">
         <v>9</v>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>10.99997240911249</v>
+        <v>10.99997240911248</v>
       </c>
       <c r="C22">
         <v>10</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>11.00000000000001</v>
+        <v>11</v>
       </c>
       <c r="C23">
         <v>11</v>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>76.34457443735987</v>
+        <v>76.34457443735988</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>15.52456228630448</v>
+        <v>15.52456228630446</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>4.725484079429664</v>
+        <v>4.725484079429673</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>2.005528177882338</v>
+        <v>2.005528177882341</v>
       </c>
       <c r="C27">
         <v>4</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.5616305015209244</v>
+        <v>0.5616305015209256</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.4548378167322993</v>
+        <v>0.4548378167323005</v>
       </c>
       <c r="C29">
         <v>6</v>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.3319396744102281</v>
+        <v>0.3319396744102278</v>
       </c>
       <c r="C30">
         <v>7</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.04941305707976455</v>
+        <v>0.04941305707976465</v>
       </c>
       <c r="C31">
         <v>8</v>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.0009765947959895602</v>
+        <v>0.0009765947959895576</v>
       </c>
       <c r="C32">
         <v>9</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.0008025482342619056</v>
+        <v>0.0008025482342618915</v>
       </c>
       <c r="C33">
         <v>10</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.0002508262501741694</v>
+        <v>0.0002508262501741735</v>
       </c>
       <c r="C34">
         <v>11</v>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>76.34457443735987</v>
+        <v>76.34457443735988</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>96.594620803094</v>
+        <v>96.59462080309402</v>
       </c>
       <c r="C37">
         <v>3</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>98.60014898097634</v>
+        <v>98.60014898097636</v>
       </c>
       <c r="C38">
         <v>4</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="B39">
-        <v>99.16177948249725</v>
+        <v>99.16177948249728</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B40">
-        <v>99.61661729922956</v>
+        <v>99.61661729922959</v>
       </c>
       <c r="C40">
         <v>6</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B41">
-        <v>99.9485569736398</v>
+        <v>99.94855697363981</v>
       </c>
       <c r="C41">
         <v>7</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B42">
-        <v>99.99797003071956</v>
+        <v>99.99797003071957</v>
       </c>
       <c r="C42">
         <v>8</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B43">
-        <v>99.99894662551554</v>
+        <v>99.99894662551557</v>
       </c>
       <c r="C43">
         <v>9</v>

--- a/03_Outputs/all/01_TablasDescriptivas/idx15_vejez_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx15_vejez_vr.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>8.397903188109588</v>
+        <v>3.637194980789653</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.707701851493491</v>
+        <v>1.646027078152126</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.5198032487372641</v>
+        <v>0.4711154997518476</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.2206080995670575</v>
+        <v>0.2196239800549294</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.06177935516730183</v>
+        <v>0.0259964555013779</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.05003215984055306</v>
+        <v>4.20057500631787E-05</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -487,14 +487,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>variance</t>
+          <t>cumulative variance</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.03651336418512506</v>
+        <v>3.637194980789653</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -505,14 +505,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>variance</t>
+          <t>cumulative variance</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.005435436278774112</v>
+        <v>5.283222058941779</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -523,14 +523,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>variance</t>
+          <t>cumulative variance</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.0001074254275588514</v>
+        <v>5.754337558693626</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -541,14 +541,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>variance</t>
+          <t>cumulative variance</t>
         </is>
       </c>
       <c r="B11">
-        <v>8.828030576880808E-05</v>
+        <v>5.973961538748556</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -559,14 +559,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>variance</t>
+          <t>cumulative variance</t>
         </is>
       </c>
       <c r="B12">
-        <v>2.759088751915909E-05</v>
+        <v>5.999957994249934</v>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -581,10 +581,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>8.397903188109588</v>
+        <v>5.999999999999997</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -595,14 +595,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cumulative variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B14">
-        <v>10.10560503960308</v>
+        <v>60.61991634649424</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -613,14 +613,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cumulative variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B15">
-        <v>10.62540828834034</v>
+        <v>27.43378463586879</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -631,14 +631,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cumulative variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B16">
-        <v>10.8460163879074</v>
+        <v>7.85192499586413</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -649,14 +649,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cumulative variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B17">
-        <v>10.9077957430747</v>
+        <v>3.660399667582158</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -667,14 +667,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cumulative variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B18">
-        <v>10.95782790291526</v>
+        <v>0.4332742583562985</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -685,14 +685,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cumulative variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B19">
-        <v>10.99434126710038</v>
+        <v>0.0007000958343863121</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -703,14 +703,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cumulative variance</t>
+          <t>cumulative percent variance</t>
         </is>
       </c>
       <c r="B20">
-        <v>10.99977670337915</v>
+        <v>60.61991634649424</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -721,14 +721,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cumulative variance</t>
+          <t>cumulative percent variance</t>
         </is>
       </c>
       <c r="B21">
-        <v>10.99988412880671</v>
+        <v>88.05370098236303</v>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cumulative variance</t>
+          <t>cumulative percent variance</t>
         </is>
       </c>
       <c r="B22">
-        <v>10.99997240911248</v>
+        <v>95.90562597822715</v>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -757,14 +757,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cumulative variance</t>
+          <t>cumulative percent variance</t>
         </is>
       </c>
       <c r="B23">
-        <v>11</v>
+        <v>99.5660256458093</v>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -775,14 +775,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>percent variance</t>
+          <t>cumulative percent variance</t>
         </is>
       </c>
       <c r="B24">
-        <v>76.34457443735988</v>
+        <v>99.99929990416561</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -793,376 +793,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>percent variance</t>
+          <t>cumulative percent variance</t>
         </is>
       </c>
       <c r="B25">
-        <v>15.52456228630446</v>
+        <v>100</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D25" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>percent variance</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>4.725484079429673</v>
-      </c>
-      <c r="C26">
-        <v>3</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>percent variance</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>2.005528177882341</v>
-      </c>
-      <c r="C27">
-        <v>4</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>percent variance</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>0.5616305015209256</v>
-      </c>
-      <c r="C28">
-        <v>5</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>percent variance</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>0.4548378167323005</v>
-      </c>
-      <c r="C29">
-        <v>6</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>percent variance</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>0.3319396744102278</v>
-      </c>
-      <c r="C30">
-        <v>7</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>percent variance</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>0.04941305707976465</v>
-      </c>
-      <c r="C31">
-        <v>8</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>percent variance</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>0.0009765947959895576</v>
-      </c>
-      <c r="C32">
-        <v>9</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>percent variance</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>0.0008025482342618915</v>
-      </c>
-      <c r="C33">
-        <v>10</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>percent variance</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>0.0002508262501741735</v>
-      </c>
-      <c r="C34">
-        <v>11</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>cumulative percent variance</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>76.34457443735988</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>cumulative percent variance</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>91.86913672366434</v>
-      </c>
-      <c r="C36">
-        <v>2</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>cumulative percent variance</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>96.59462080309402</v>
-      </c>
-      <c r="C37">
-        <v>3</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>cumulative percent variance</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>98.60014898097636</v>
-      </c>
-      <c r="C38">
-        <v>4</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>cumulative percent variance</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>99.16177948249728</v>
-      </c>
-      <c r="C39">
-        <v>5</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>cumulative percent variance</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>99.61661729922959</v>
-      </c>
-      <c r="C40">
-        <v>6</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>cumulative percent variance</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>99.94855697363981</v>
-      </c>
-      <c r="C41">
-        <v>7</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>cumulative percent variance</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>99.99797003071957</v>
-      </c>
-      <c r="C42">
-        <v>8</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>cumulative percent variance</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>99.99894662551557</v>
-      </c>
-      <c r="C43">
-        <v>9</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>cumulative percent variance</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>99.99974917374982</v>
-      </c>
-      <c r="C44">
-        <v>10</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>pca</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>cumulative percent variance</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>100</v>
-      </c>
-      <c r="C45">
-        <v>11</v>
-      </c>
-      <c r="D45" t="inlineStr">
         <is>
           <t>pca</t>
         </is>

--- a/03_Outputs/all/01_TablasDescriptivas/idx15_vejez_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx15_vejez_vr.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>3.637194980789653</v>
+        <v>6.202164971681897</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.646027078152126</v>
+        <v>1.717932685633907</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.4711154997518476</v>
+        <v>0.5175319665908661</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.2196239800549294</v>
+        <v>0.2898573923114844</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.0259964555013779</v>
+        <v>0.2156338786881721</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>4.20057500631787E-05</v>
+        <v>0.03009143878586542</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -487,14 +487,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cumulative variance</t>
+          <t>variance</t>
         </is>
       </c>
       <c r="B8">
-        <v>3.637194980789653</v>
+        <v>0.01936078675368071</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -505,14 +505,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cumulative variance</t>
+          <t>variance</t>
         </is>
       </c>
       <c r="B9">
-        <v>5.283222058941779</v>
+        <v>0.00739542831141655</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -523,14 +523,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cumulative variance</t>
+          <t>variance</t>
         </is>
       </c>
       <c r="B10">
-        <v>5.754337558693626</v>
+        <v>3.145124273266758E-05</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -545,10 +545,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>5.973961538748556</v>
+        <v>6.202164971681897</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>5.999957994249934</v>
+        <v>7.920097657315804</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -581,10 +581,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>5.999999999999997</v>
+        <v>8.43762962390667</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -595,14 +595,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>percent variance</t>
+          <t>cumulative variance</t>
         </is>
       </c>
       <c r="B14">
-        <v>60.61991634649424</v>
+        <v>8.727487016218154</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -613,14 +613,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>percent variance</t>
+          <t>cumulative variance</t>
         </is>
       </c>
       <c r="B15">
-        <v>27.43378463586879</v>
+        <v>8.943120894906327</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -631,14 +631,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>percent variance</t>
+          <t>cumulative variance</t>
         </is>
       </c>
       <c r="B16">
-        <v>7.85192499586413</v>
+        <v>8.973212333692192</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -649,14 +649,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>percent variance</t>
+          <t>cumulative variance</t>
         </is>
       </c>
       <c r="B17">
-        <v>3.660399667582158</v>
+        <v>8.992573120445872</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -667,14 +667,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>percent variance</t>
+          <t>cumulative variance</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.4332742583562985</v>
+        <v>8.999968548757289</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -685,14 +685,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>percent variance</t>
+          <t>cumulative variance</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.0007000958343863121</v>
+        <v>9.000000000000021</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cumulative percent variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B20">
-        <v>60.61991634649424</v>
+        <v>68.91294412979869</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -721,11 +721,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cumulative percent variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B21">
-        <v>88.05370098236303</v>
+        <v>19.08814095148781</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -739,11 +739,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cumulative percent variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B22">
-        <v>95.90562597822715</v>
+        <v>5.750355184342943</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -757,11 +757,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cumulative percent variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B23">
-        <v>99.5660256458093</v>
+        <v>3.220637692349819</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -775,11 +775,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cumulative percent variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B24">
-        <v>99.99929990416561</v>
+        <v>2.395931985424129</v>
       </c>
       <c r="C24">
         <v>5</v>
@@ -793,16 +793,232 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cumulative percent variance</t>
+          <t>percent variance</t>
         </is>
       </c>
       <c r="B25">
-        <v>100</v>
+        <v>0.3343493198429483</v>
       </c>
       <c r="C25">
         <v>6</v>
       </c>
       <c r="D25" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>percent variance</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>0.215119852818674</v>
+      </c>
+      <c r="C26">
+        <v>7</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>percent variance</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>0.0821714256824059</v>
+      </c>
+      <c r="C27">
+        <v>8</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>percent variance</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>0.0003494582525851946</v>
+      </c>
+      <c r="C28">
+        <v>9</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cumulative percent variance</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>68.91294412979869</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cumulative percent variance</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>88.0010850812865</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cumulative percent variance</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>93.75144026562944</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cumulative percent variance</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>96.97207795797927</v>
+      </c>
+      <c r="C32">
+        <v>4</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cumulative percent variance</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>99.36800994340341</v>
+      </c>
+      <c r="C33">
+        <v>5</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cumulative percent variance</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>99.70235926324634</v>
+      </c>
+      <c r="C34">
+        <v>6</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cumulative percent variance</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>99.91747911606501</v>
+      </c>
+      <c r="C35">
+        <v>7</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cumulative percent variance</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>99.99965054174741</v>
+      </c>
+      <c r="C36">
+        <v>8</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>pca</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cumulative percent variance</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>100</v>
+      </c>
+      <c r="C37">
+        <v>9</v>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>pca</t>
         </is>
